--- a/Assessment Questions/CDA/STA-139/EXPLORATORY DATA ANALYSIS/Measures Of Distance_ Euclidean,/Measures Of Distance_ Euclidean,.xlsx
+++ b/Assessment Questions/CDA/STA-139/EXPLORATORY DATA ANALYSIS/Measures Of Distance_ Euclidean,/Measures Of Distance_ Euclidean,.xlsx
@@ -1,98 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>Find Euclidean distance between (2,3) and (5,7).</t>
-  </si>
-  <si>
-    <t>Find Manhattan distance between (1,2) and (4,6).</t>
-  </si>
-  <si>
-    <t>What is Minkowski distance?</t>
-  </si>
-  <si>
-    <t>When p = 2, Minkowski becomes what?</t>
-  </si>
-  <si>
-    <t>When p = 1, Minkowski becomes what?</t>
-  </si>
-  <si>
-    <t>Why Euclidean distance is commonly used?</t>
-  </si>
-  <si>
-    <t>Manhattan distance is useful in which scenarios?</t>
-  </si>
-  <si>
-    <t>Calculate Euclidean distance in 3D space.</t>
-  </si>
-  <si>
-    <t>Which distance is used in KNN?</t>
-  </si>
-  <si>
-    <t>What happens when p → ∞ in Minkowski?</t>
-  </si>
-  <si>
-    <t>Why Manhattan distance works better in grids?</t>
-  </si>
-  <si>
-    <t>Which distance is sensitive to outliers?</t>
-  </si>
-  <si>
-    <t>Compare Euclidean vs Manhattan.</t>
-  </si>
-  <si>
-    <t>Why normalize data before distance calculation?</t>
-  </si>
-  <si>
-    <t>What is distance metric?</t>
-  </si>
-  <si>
-    <t>In clustering, why distance matters?</t>
-  </si>
-  <si>
-    <t>Which distance is faster to compute?</t>
-  </si>
-  <si>
-    <t>What is curse of dimensionality?</t>
-  </si>
-  <si>
-    <t>How does distance behave in high dimensions?</t>
-  </si>
-  <si>
-    <t>Which distance to use for sparse data?</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -102,29 +38,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -322,113 +315,587 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Measures Of Distance_ Euclidean,</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>Find Euclidean distance between (2,3) and (5,7).</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr"/>
+      <c r="F2" s="0" t="inlineStr"/>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Measures Of Distance_ Euclidean,</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>Find Manhattan distance between (1,2) and (4,6).</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr"/>
+      <c r="F3" s="0" t="inlineStr"/>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Measures Of Distance_ Euclidean,</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>What is Minkowski distance?</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr"/>
+      <c r="F4" s="0" t="inlineStr"/>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Measures Of Distance_ Euclidean,</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>When p = 2, Minkowski becomes what?</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr"/>
+      <c r="F5" s="0" t="inlineStr"/>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Measures Of Distance_ Euclidean,</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>When p = 1, Minkowski becomes what?</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr"/>
+      <c r="F6" s="0" t="inlineStr"/>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Measures Of Distance_ Euclidean,</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>Why Euclidean distance is commonly used?</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr"/>
+      <c r="F7" s="0" t="inlineStr"/>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="0" t="n">
         <v>7</v>
       </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Measures Of Distance_ Euclidean,</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>Manhattan distance is useful in which scenarios?</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr"/>
+      <c r="F8" s="0" t="inlineStr"/>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="0" t="n">
         <v>8</v>
       </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Measures Of Distance_ Euclidean,</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>Calculate Euclidean distance in 3D space.</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr"/>
+      <c r="F9" s="0" t="inlineStr"/>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="0" t="n">
         <v>9</v>
       </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Measures Of Distance_ Euclidean,</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>Which distance is used in KNN?</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr"/>
+      <c r="F10" s="0" t="inlineStr"/>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Measures Of Distance_ Euclidean,</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>What happens when p → ∞ in Minkowski?</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr"/>
+      <c r="F11" s="0" t="inlineStr"/>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="n">
         <v>11</v>
       </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Measures Of Distance_ Euclidean,</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>Why Manhattan distance works better in grids?</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr"/>
+      <c r="F12" s="0" t="inlineStr"/>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Measures Of Distance_ Euclidean,</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>Which distance is sensitive to outliers?</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr"/>
+      <c r="F13" s="0" t="inlineStr"/>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="0" t="n">
         <v>13</v>
       </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Measures Of Distance_ Euclidean,</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>Compare Euclidean vs Manhattan.</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr"/>
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="0" t="n">
         <v>14</v>
       </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Measures Of Distance_ Euclidean,</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Why normalize data before distance calculation?</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr"/>
+      <c r="F15" s="0" t="inlineStr"/>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="0" t="n">
         <v>15</v>
       </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Measures Of Distance_ Euclidean,</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>What is distance metric?</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr"/>
+      <c r="F16" s="0" t="inlineStr"/>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="0" t="n">
         <v>16</v>
       </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Measures Of Distance_ Euclidean,</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>In clustering, why distance matters?</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr"/>
+      <c r="F17" s="0" t="inlineStr"/>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="0" t="n">
         <v>17</v>
       </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>Measures Of Distance_ Euclidean,</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>Which distance is faster to compute?</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr"/>
+      <c r="F18" s="0" t="inlineStr"/>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="0" t="n">
         <v>18</v>
       </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Measures Of Distance_ Euclidean,</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>What is curse of dimensionality?</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr"/>
+      <c r="F19" s="0" t="inlineStr"/>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="0" t="n">
         <v>19</v>
       </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Measures Of Distance_ Euclidean,</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>How does distance behave in high dimensions?</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr"/>
+      <c r="F20" s="0" t="inlineStr"/>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Measures Of Distance_ Euclidean,</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Which distance to use for sparse data?</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr"/>
+      <c r="F21" s="0" t="inlineStr"/>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>